--- a/data/30August-89ers-v-Gold_Diggers.xlsx
+++ b/data/30August-89ers-v-Gold_Diggers.xlsx
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O124"/>
   <sheetData>
     <row r="1">
@@ -332,8 +332,10 @@
       <c r="D10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="L10" t="s">
         <v>22</v>
@@ -539,8 +541,10 @@
       <c r="D31" t="s">
         <v>18</v>
       </c>
-      <c r="E31" t="s">
-        <v>21</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -973,8 +977,10 @@
       <c r="D77" t="s">
         <v>18</v>
       </c>
-      <c r="E77" t="s">
-        <v>45</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LCDC</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1124,8 +1130,10 @@
       <c r="D94" t="s">
         <v>48</v>
       </c>
-      <c r="E94" t="s">
-        <v>49</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -1257,8 +1265,10 @@
       <c r="D108" t="s">
         <v>18</v>
       </c>
-      <c r="E108" t="s">
-        <v>21</v>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="109">
